--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.55141414638563</v>
+        <v>5.289604798787665</v>
       </c>
       <c r="D2" t="n">
-        <v>45.3271569998256</v>
+        <v>7.36566301247166</v>
       </c>
       <c r="E2" t="n">
-        <v>10.54687807979593</v>
+        <v>1.71386768796684</v>
       </c>
       <c r="F2" t="n">
-        <v>12.46733003809771</v>
+        <v>2.025941131190877</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.99484322570373</v>
+        <v>7.474162024176856</v>
       </c>
       <c r="D3" t="n">
-        <v>51.62310529210733</v>
+        <v>8.388754609967441</v>
       </c>
       <c r="E3" t="n">
-        <v>10.54687807979593</v>
+        <v>1.71386768796684</v>
       </c>
       <c r="F3" t="n">
-        <v>12.46733003809771</v>
+        <v>2.025941131190877</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.36149680570765</v>
+        <v>6.396243230927494</v>
       </c>
       <c r="D4" t="n">
-        <v>45.49664822819368</v>
+        <v>7.393205337081474</v>
       </c>
       <c r="E4" t="n">
-        <v>10.54687807979593</v>
+        <v>1.71386768796684</v>
       </c>
       <c r="F4" t="n">
-        <v>12.46733003809771</v>
+        <v>2.025941131190877</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.48790848805037</v>
+        <v>3.166785129308185</v>
       </c>
       <c r="D5" t="n">
-        <v>30.67986195269689</v>
+        <v>4.985477567313244</v>
       </c>
       <c r="E5" t="n">
-        <v>10.54687807979593</v>
+        <v>1.71386768796684</v>
       </c>
       <c r="F5" t="n">
-        <v>12.46733003809771</v>
+        <v>2.025941131190877</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.76302628769641</v>
+        <v>6.298991771750667</v>
       </c>
       <c r="D6" t="n">
-        <v>38.53605734957045</v>
+        <v>6.262109319305198</v>
       </c>
       <c r="E6" t="n">
-        <v>10.54687807979593</v>
+        <v>1.71386768796684</v>
       </c>
       <c r="F6" t="n">
-        <v>12.46733003809771</v>
+        <v>2.025941131190877</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.75939373913585</v>
+        <v>4.673401482609575</v>
       </c>
       <c r="D7" t="n">
-        <v>28.83998959777898</v>
+        <v>4.686498309639084</v>
       </c>
       <c r="E7" t="n">
-        <v>10.54687807979593</v>
+        <v>1.71386768796684</v>
       </c>
       <c r="F7" t="n">
-        <v>12.46733003809771</v>
+        <v>2.025941131190877</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.06026944768056</v>
+        <v>2.772293785248091</v>
       </c>
       <c r="D8" t="n">
-        <v>18.08619855173173</v>
+        <v>2.939007264656407</v>
       </c>
       <c r="E8" t="n">
-        <v>10.54687807979593</v>
+        <v>1.71386768796684</v>
       </c>
       <c r="F8" t="n">
-        <v>12.46733003809771</v>
+        <v>2.025941131190877</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.60006029588472</v>
+        <v>3.510009798081267</v>
       </c>
       <c r="D9" t="n">
-        <v>20.76643927109316</v>
+        <v>3.374546381552638</v>
       </c>
       <c r="E9" t="n">
-        <v>10.54687807979593</v>
+        <v>1.71386768796684</v>
       </c>
       <c r="F9" t="n">
-        <v>12.46733003809771</v>
+        <v>2.025941131190877</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>8.509889633069786</v>
+        <v>1.38285706537384</v>
       </c>
       <c r="D10" t="n">
-        <v>35.13860087004926</v>
+        <v>5.710022641383005</v>
       </c>
       <c r="E10" t="n">
-        <v>10.54687807979593</v>
+        <v>1.71386768796684</v>
       </c>
       <c r="F10" t="n">
-        <v>12.46733003809771</v>
+        <v>2.025941131190877</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.44836442955664</v>
+        <v>4.460359219802955</v>
       </c>
       <c r="D11" t="n">
-        <v>11.53232127294627</v>
+        <v>1.874002206853769</v>
       </c>
       <c r="E11" t="n">
-        <v>10.54687807979593</v>
+        <v>1.71386768796684</v>
       </c>
       <c r="F11" t="n">
-        <v>12.46733003809771</v>
+        <v>2.025941131190877</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.68266211166814</v>
+        <v>5.310932593146074</v>
       </c>
       <c r="D12" t="n">
-        <v>19.10766635716417</v>
+        <v>3.104995783039178</v>
       </c>
       <c r="E12" t="n">
-        <v>10.54687807979593</v>
+        <v>1.71386768796684</v>
       </c>
       <c r="F12" t="n">
-        <v>12.46733003809771</v>
+        <v>2.025941131190877</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
